--- a/data/inversiones/prestamos.xlsx
+++ b/data/inversiones/prestamos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Adrian\Bots\FinancialAgent\data\inversiones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codigos\FinancialAgent\data\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA89520-8575-4D3C-B6D3-E023D1FB7710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BC90FE-52E4-40B9-87E6-A911478C129B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Préstamos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Prestatario</t>
   </si>
@@ -34,19 +34,13 @@
     <t>Plazo</t>
   </si>
   <si>
-    <t>Interés Esperado</t>
-  </si>
-  <si>
-    <t>Retorno Total</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
-    <t>Fecha Vencimiento</t>
-  </si>
-  <si>
-    <t>activo</t>
+    <t>Adrian</t>
+  </si>
+  <si>
+    <t>En curso</t>
   </si>
 </sst>
 </file>
@@ -386,10 +380,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -405,30 +399,39 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>200</v>
       </c>
-      <c r="G2" t="s">
-        <v>8</v>
+      <c r="C2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
       <c r="B3">
         <v>200</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
+      <c r="C3">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D3">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
